--- a/outputs/experiment_summary.xlsx
+++ b/outputs/experiment_summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shivi\Desktop\BITS BA Course\Capstone Project\part2_kpi_experiment\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97C539A9-198B-4924-962C-BD728EFB7B77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7116F627-40BB-44E8-890B-037D5E6AC175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="7" xr2:uid="{646B14BA-5C32-4B93-90F9-3681B8ABEB50}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="6" xr2:uid="{646B14BA-5C32-4B93-90F9-3681B8ABEB50}"/>
   </bookViews>
   <sheets>
     <sheet name="experiment_data" sheetId="2" r:id="rId1"/>
@@ -4497,7 +4497,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="176" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -4584,7 +4584,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4616,25 +4616,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" pivotButton="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4643,39 +4631,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="61">
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
     <dxf>
       <alignment horizontal="center"/>
     </dxf>
@@ -5380,6 +5372,15 @@
           <color indexed="64"/>
         </horizontal>
       </border>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -33937,68 +33938,68 @@
     <dataField name="Count of user_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="16">
-    <format dxfId="47">
+    <format dxfId="60">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="46">
+    <format dxfId="59">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="45">
+    <format dxfId="58">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="44">
+    <format dxfId="57">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="43">
+    <format dxfId="56">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="42">
+    <format dxfId="55">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="41">
+    <format dxfId="54">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="40">
+    <format dxfId="53">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="39">
+    <format dxfId="52">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="38">
+    <format dxfId="51">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="37">
+    <format dxfId="50">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="36">
+    <format dxfId="49">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="35">
+    <format dxfId="48">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="34">
+    <format dxfId="47">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="33">
+    <format dxfId="46">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="32">
+    <format dxfId="45">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -34087,68 +34088,68 @@
     <dataField name="Count of user_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="16">
-    <format dxfId="31">
+    <format dxfId="44">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="30">
+    <format dxfId="43">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="29">
+    <format dxfId="42">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="28">
+    <format dxfId="41">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="27">
+    <format dxfId="40">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="39">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="25">
+    <format dxfId="38">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="24">
+    <format dxfId="37">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="23">
+    <format dxfId="36">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="22">
+    <format dxfId="35">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="21">
+    <format dxfId="34">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="20">
+    <format dxfId="33">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="19">
+    <format dxfId="32">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="18">
+    <format dxfId="31">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="17">
+    <format dxfId="30">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="16">
+    <format dxfId="29">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -34245,68 +34246,68 @@
     <dataField name="Count of user_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="16">
-    <format dxfId="15">
+    <format dxfId="28">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="14">
+    <format dxfId="27">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="13">
+    <format dxfId="26">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="12">
+    <format dxfId="25">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="11">
+    <format dxfId="24">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="10">
+    <format dxfId="23">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="9">
+    <format dxfId="22">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="5" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="8">
+    <format dxfId="21">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="7">
+    <format dxfId="20">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="6">
+    <format dxfId="19">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="5">
+    <format dxfId="18">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="4">
+    <format dxfId="17">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="3">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="2">
+    <format dxfId="15">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="1">
+    <format dxfId="14">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="0">
+    <format dxfId="13">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -34391,55 +34392,55 @@
     <dataField name="Count of user_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="13">
-    <format dxfId="60">
+    <format dxfId="12">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="59">
+    <format dxfId="11">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="58">
+    <format dxfId="10">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="57">
+    <format dxfId="9">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="56">
+    <format dxfId="8">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="55">
+    <format dxfId="7">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="54">
+    <format dxfId="6">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="53">
+    <format dxfId="5">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="52">
+    <format dxfId="4">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="51">
+    <format dxfId="3">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="50">
+    <format dxfId="2">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="49">
+    <format dxfId="1">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="48">
+    <format dxfId="0">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -101381,30 +101382,30 @@
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="24" t="s">
         <v>1451</v>
       </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="23" t="s">
         <v>1452</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -101522,30 +101523,30 @@
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="24" t="s">
         <v>1451</v>
       </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="25" t="s">
         <v>1453</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -101690,36 +101691,36 @@
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="24" t="s">
         <v>1454</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="24"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="26" t="s">
         <v>1455</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -101822,36 +101823,36 @@
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="24" t="s">
         <v>1454</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="24"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="26" t="s">
         <v>1456</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -101864,107 +101865,110 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88079CE1-1B64-4B58-8454-536EF1F798DB}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="18.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.36328125" customWidth="1"/>
     <col min="7" max="7" width="12.36328125" customWidth="1"/>
+    <col min="9" max="9" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="16">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:9" ht="16">
+      <c r="A1" s="27" t="s">
         <v>1470</v>
       </c>
-      <c r="B1" s="25"/>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="20" t="s">
+      <c r="B1" s="27"/>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="16" t="s">
         <v>1457</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="16">
         <v>693</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="20" t="s">
+    <row r="4" spans="1:9">
+      <c r="A4" s="16" t="s">
         <v>1458</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="16">
         <v>108</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="20" t="s">
+    <row r="5" spans="1:9">
+      <c r="A5" s="16" t="s">
         <v>1459</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="16">
         <v>715</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="20" t="s">
+    <row r="6" spans="1:9">
+      <c r="A6" s="16" t="s">
         <v>1460</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="16">
         <v>152</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:9">
       <c r="A8" s="7" t="s">
         <v>1461</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="13">
         <f>B4/B3</f>
         <v>0.15584415584415584</v>
       </c>
-    </row>
-    <row r="9" spans="1:2">
+      <c r="I8" s="28"/>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="7" t="s">
         <v>1462</v>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="13">
         <f>B6/B5</f>
         <v>0.21258741258741259</v>
       </c>
-    </row>
-    <row r="10" spans="1:2">
+      <c r="I9" s="28"/>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="7" t="s">
         <v>1463</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="13">
         <f>(B4+B6)/(B3+B5)</f>
         <v>0.18465909090909091</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:9">
       <c r="A11" s="7" t="s">
         <v>1464</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="13">
         <f>SQRT(B10*(1-B10)*(1/B3+1/B5))</f>
         <v>2.0684101126282654E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:9">
       <c r="A12" s="7" t="s">
         <v>1465</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="14">
         <f>(B9-B8)/B11</f>
         <v>2.7433271765991725</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:9">
       <c r="A13" s="10" t="s">
         <v>1466</v>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="15">
         <f>1-_xlfn.NORM.S.DIST(B12,TRUE)</f>
         <v>3.0410026809165602E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:9">
       <c r="A14" s="7" t="s">
         <v>1467</v>
       </c>
@@ -101974,16 +101978,16 @@
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="21" t="s">
         <v>1468</v>
       </c>
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="23"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
     </row>
     <row r="18" spans="1:8" ht="14.5" customHeight="1">
       <c r="A18" s="22" t="s">
@@ -102028,14 +102032,14 @@
       <c r="H21" s="22"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="23" t="s">
+      <c r="A23" s="21" t="s">
         <v>1472</v>
       </c>
-      <c r="B23" s="23"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="22" t="s">
@@ -102081,16 +102085,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="24" t="s">
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="18" t="s">
         <v>1473</v>
       </c>
     </row>
@@ -102098,10 +102102,10 @@
       <c r="A2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="26">
-        <v>0</v>
-      </c>
-      <c r="C2" s="26">
+      <c r="B2" s="19">
+        <v>0</v>
+      </c>
+      <c r="C2" s="19">
         <v>4.1999999999999997E-3</v>
       </c>
       <c r="D2" s="7" t="s">
@@ -102112,10 +102116,10 @@
       <c r="A3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="19">
         <v>0.1472</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="19">
         <v>0.24759999999999999</v>
       </c>
       <c r="D3" s="7" t="s">
@@ -102165,16 +102169,16 @@
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="21" t="s">
         <v>1478</v>
       </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
     </row>
     <row r="10" spans="1:10" ht="14.5" customHeight="1">
       <c r="A10" s="22" t="s">
@@ -102187,8 +102191,8 @@
       <c r="F10" s="22"/>
       <c r="G10" s="22"/>
       <c r="H10" s="22"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="22"/>
@@ -102199,8 +102203,8 @@
       <c r="F11" s="22"/>
       <c r="G11" s="22"/>
       <c r="H11" s="22"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="22"/>
@@ -102233,14 +102237,14 @@
       <c r="H14" s="22"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="27"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="2">
